--- a/app/templates_excel/nigredo/n8_en.xlsx
+++ b/app/templates_excel/nigredo/n8_en.xlsx
@@ -1325,10 +1325,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>A pagent.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>A man makes a futuristic drawing.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1389,10 +1385,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>A tree feiled and sawed.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>A church bazaar.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1517,10 +1509,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>A window at an open grave.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>A bridge being built across a gorge.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1737,10 +1725,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Chinese woman nusing a baby with a message.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>A group of people who have overeaten and enjoyed it.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2509,10 +2493,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>A gigatic tent.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>A master instructing his pupil.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2533,10 +2513,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>An inhibited island.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>The purging of the priesthood.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2622,6 +2598,30 @@
   </si>
   <si>
     <t>A gang of robbers in hiding.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A widow at an open grave.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Chinese woman nursing a baby with a message.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A tree felled and sawed.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A gigantic tent.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>An inhabited island.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A pageant.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3510,7 +3510,7 @@
         <v>355</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3542,7 +3542,7 @@
         <v>3</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3550,7 +3550,7 @@
         <v>4</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="15" x14ac:dyDescent="0.3">
@@ -3558,7 +3558,7 @@
         <v>5</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="15" x14ac:dyDescent="0.3">
@@ -3566,7 +3566,7 @@
         <v>6</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="15" x14ac:dyDescent="0.3">
@@ -3574,7 +3574,7 @@
         <v>7</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="15" x14ac:dyDescent="0.3">
@@ -3582,7 +3582,7 @@
         <v>8</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="15" x14ac:dyDescent="0.3">
@@ -3590,7 +3590,7 @@
         <v>9</v>
       </c>
       <c r="H21" s="8" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="15" x14ac:dyDescent="0.3">
@@ -3598,7 +3598,7 @@
         <v>10</v>
       </c>
       <c r="H22" s="8" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="15" x14ac:dyDescent="0.3">
@@ -3606,146 +3606,146 @@
         <v>11</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A24" s="7" t="s">
         <v>12</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A25" s="7" t="s">
         <v>13</v>
       </c>
       <c r="H25" s="8" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A26" s="7" t="s">
         <v>14</v>
       </c>
       <c r="H26" s="8" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A27" s="7" t="s">
         <v>15</v>
       </c>
       <c r="H27" s="8" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A28" s="7" t="s">
         <v>16</v>
       </c>
       <c r="H28" s="8" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A29" s="7" t="s">
         <v>17</v>
       </c>
       <c r="H29" s="8" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A30" s="7" t="s">
         <v>18</v>
       </c>
       <c r="H30" s="8" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A31" s="7" t="s">
         <v>19</v>
       </c>
       <c r="H31" s="8" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A32" s="7" t="s">
         <v>20</v>
       </c>
       <c r="H32" s="8" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A33" s="7" t="s">
         <v>21</v>
       </c>
       <c r="H33" s="8" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A34" s="7" t="s">
         <v>22</v>
       </c>
       <c r="H34" s="8" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A35" s="7" t="s">
         <v>23</v>
       </c>
       <c r="H35" s="8" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A36" s="7" t="s">
         <v>24</v>
       </c>
       <c r="H36" s="8" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A37" s="7" t="s">
         <v>25</v>
       </c>
       <c r="H37" s="8" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A38" s="7" t="s">
         <v>26</v>
       </c>
       <c r="H38" s="8" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A39" s="7" t="s">
         <v>27</v>
       </c>
       <c r="H39" s="8" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A40" s="7" t="s">
         <v>377</v>
       </c>
       <c r="H40" s="8" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" s="9" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" s="9" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B41" s="9" t="s">
         <v>372</v>
       </c>
@@ -3771,31 +3771,31 @@
         <v>375</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A42" s="10" t="s">
         <v>357</v>
       </c>
       <c r="H42" s="8" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A43" s="10" t="s">
         <v>358</v>
       </c>
       <c r="H43" s="8" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A44" s="10" t="s">
         <v>28</v>
       </c>
       <c r="H44" s="8" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A45" s="10" t="s">
         <v>29</v>
       </c>
@@ -3803,47 +3803,47 @@
         <v>406</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A46" s="10" t="s">
         <v>30</v>
       </c>
       <c r="H46" s="8" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A47" s="10" t="s">
         <v>31</v>
       </c>
       <c r="H47" s="8" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A48" s="10" t="s">
         <v>32</v>
       </c>
       <c r="H48" s="8" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A49" s="10" t="s">
         <v>33</v>
       </c>
       <c r="H49" s="8" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A50" s="10" t="s">
         <v>34</v>
       </c>
       <c r="H50" s="8" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A51" s="10" t="s">
         <v>35</v>
       </c>
@@ -3851,31 +3851,31 @@
         <v>405</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A52" s="10" t="s">
         <v>36</v>
       </c>
       <c r="H52" s="8" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A53" s="10" t="s">
         <v>37</v>
       </c>
       <c r="H53" s="8" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A54" s="10" t="s">
         <v>38</v>
       </c>
       <c r="H54" s="8" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A55" s="10" t="s">
         <v>39</v>
       </c>
@@ -3883,39 +3883,39 @@
         <v>404</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A56" s="10" t="s">
         <v>40</v>
       </c>
       <c r="H56" s="8" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A57" s="10" t="s">
         <v>41</v>
       </c>
       <c r="H57" s="8" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A58" s="10" t="s">
         <v>42</v>
       </c>
       <c r="H58" s="8" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A59" s="10" t="s">
         <v>43</v>
       </c>
       <c r="H59" s="8" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A60" s="10" t="s">
         <v>44</v>
       </c>
@@ -3923,55 +3923,55 @@
         <v>403</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A61" s="10" t="s">
         <v>45</v>
       </c>
       <c r="H61" s="8" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A62" s="10" t="s">
         <v>46</v>
       </c>
       <c r="H62" s="8" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A63" s="10" t="s">
         <v>47</v>
       </c>
       <c r="H63" s="8" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A64" s="10" t="s">
         <v>48</v>
       </c>
       <c r="H64" s="8" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A65" s="10" t="s">
         <v>49</v>
       </c>
       <c r="H65" s="8" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="66" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A66" s="10" t="s">
         <v>50</v>
       </c>
       <c r="H66" s="8" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A67" s="10" t="s">
         <v>51</v>
       </c>
@@ -3979,39 +3979,39 @@
         <v>402</v>
       </c>
     </row>
-    <row r="68" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A68" s="10" t="s">
         <v>52</v>
       </c>
       <c r="H68" s="8" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="69" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A69" s="10" t="s">
         <v>53</v>
       </c>
       <c r="H69" s="8" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="70" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A70" s="10" t="s">
         <v>54</v>
       </c>
       <c r="H70" s="8" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="71" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A71" s="10" t="s">
         <v>55</v>
       </c>
       <c r="H71" s="8" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="72" spans="1:9" s="9" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" s="9" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B72" s="9" t="s">
         <v>372</v>
       </c>
@@ -4037,31 +4037,31 @@
         <v>375</v>
       </c>
     </row>
-    <row r="73" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A73" s="11" t="s">
         <v>359</v>
       </c>
       <c r="H73" s="8" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="74" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A74" s="11" t="s">
         <v>360</v>
       </c>
       <c r="H74" s="8" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="75" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A75" s="11" t="s">
         <v>56</v>
       </c>
       <c r="H75" s="8" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="76" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A76" s="11" t="s">
         <v>57</v>
       </c>
@@ -4069,47 +4069,47 @@
         <v>407</v>
       </c>
     </row>
-    <row r="77" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A77" s="11" t="s">
         <v>58</v>
       </c>
       <c r="H77" s="8" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="78" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A78" s="11" t="s">
         <v>59</v>
       </c>
       <c r="H78" s="8" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="79" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A79" s="11" t="s">
         <v>60</v>
       </c>
       <c r="H79" s="8" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="80" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A80" s="11" t="s">
         <v>61</v>
       </c>
       <c r="H80" s="8" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A81" s="11" t="s">
         <v>62</v>
       </c>
       <c r="H81" s="8" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A82" s="11" t="s">
         <v>63</v>
       </c>
@@ -4117,47 +4117,47 @@
         <v>409</v>
       </c>
     </row>
-    <row r="83" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A83" s="11" t="s">
         <v>64</v>
       </c>
       <c r="H83" s="8" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A84" s="11" t="s">
         <v>65</v>
       </c>
       <c r="H84" s="8" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A85" s="11" t="s">
         <v>66</v>
       </c>
       <c r="H85" s="8" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A86" s="11" t="s">
         <v>67</v>
       </c>
       <c r="H86" s="8" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A87" s="11" t="s">
         <v>68</v>
       </c>
       <c r="H87" s="8" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A88" s="11" t="s">
         <v>69</v>
       </c>
@@ -4165,119 +4165,119 @@
         <v>408</v>
       </c>
     </row>
-    <row r="89" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A89" s="11" t="s">
         <v>70</v>
       </c>
       <c r="H89" s="8" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="90" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A90" s="11" t="s">
         <v>71</v>
       </c>
       <c r="H90" s="8" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="91" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A91" s="11" t="s">
         <v>72</v>
       </c>
       <c r="H91" s="8" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="92" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A92" s="11" t="s">
         <v>73</v>
       </c>
       <c r="H92" s="8" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="93" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A93" s="11" t="s">
         <v>74</v>
       </c>
       <c r="H93" s="8" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="94" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A94" s="11" t="s">
         <v>75</v>
       </c>
       <c r="H94" s="8" t="s">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="95" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A95" s="11" t="s">
         <v>76</v>
       </c>
       <c r="H95" s="8" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="96" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A96" s="11" t="s">
         <v>77</v>
       </c>
       <c r="H96" s="8" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="97" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A97" s="11" t="s">
         <v>78</v>
       </c>
       <c r="H97" s="8" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="98" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A98" s="11" t="s">
         <v>79</v>
       </c>
       <c r="H98" s="8" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="99" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A99" s="11" t="s">
         <v>80</v>
       </c>
       <c r="H99" s="8" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="100" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A100" s="11" t="s">
         <v>81</v>
       </c>
       <c r="H100" s="8" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="101" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A101" s="11" t="s">
         <v>82</v>
       </c>
       <c r="H101" s="8" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="102" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A102" s="11" t="s">
         <v>83</v>
       </c>
       <c r="H102" s="8" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="103" spans="1:9" s="9" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" s="9" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B103" s="9" t="s">
         <v>372</v>
       </c>
@@ -4303,31 +4303,31 @@
         <v>375</v>
       </c>
     </row>
-    <row r="104" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A104" s="12" t="s">
         <v>361</v>
       </c>
       <c r="H104" s="8" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="105" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A105" s="12" t="s">
         <v>84</v>
       </c>
       <c r="H105" s="8" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="106" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A106" s="12" t="s">
         <v>85</v>
       </c>
       <c r="H106" s="8" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="107" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A107" s="12" t="s">
         <v>86</v>
       </c>
@@ -4335,39 +4335,39 @@
         <v>410</v>
       </c>
     </row>
-    <row r="108" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A108" s="12" t="s">
         <v>87</v>
       </c>
       <c r="H108" s="8" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="109" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A109" s="12" t="s">
         <v>88</v>
       </c>
       <c r="H109" s="8" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="110" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A110" s="12" t="s">
         <v>89</v>
       </c>
       <c r="H110" s="8" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="111" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A111" s="12" t="s">
         <v>90</v>
       </c>
       <c r="H111" s="8" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="112" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A112" s="12" t="s">
         <v>91</v>
       </c>
@@ -4375,7 +4375,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="113" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A113" s="12" t="s">
         <v>92</v>
       </c>
@@ -4383,23 +4383,23 @@
         <v>381</v>
       </c>
     </row>
-    <row r="114" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A114" s="12" t="s">
         <v>93</v>
       </c>
       <c r="H114" s="8" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="115" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A115" s="12" t="s">
         <v>94</v>
       </c>
       <c r="H115" s="8" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="116" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A116" s="12" t="s">
         <v>95</v>
       </c>
@@ -4407,7 +4407,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="117" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A117" s="12" t="s">
         <v>96</v>
       </c>
@@ -4415,39 +4415,39 @@
         <v>378</v>
       </c>
     </row>
-    <row r="118" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A118" s="12" t="s">
         <v>97</v>
       </c>
       <c r="H118" s="8" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="119" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A119" s="12" t="s">
         <v>98</v>
       </c>
       <c r="H119" s="8" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="120" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A120" s="12" t="s">
         <v>99</v>
       </c>
       <c r="H120" s="8" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="121" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A121" s="12" t="s">
         <v>100</v>
       </c>
       <c r="H121" s="8" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="122" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A122" s="12" t="s">
         <v>101</v>
       </c>
@@ -4455,23 +4455,23 @@
         <v>379</v>
       </c>
     </row>
-    <row r="123" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A123" s="12" t="s">
         <v>102</v>
       </c>
       <c r="H123" s="8" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="124" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A124" s="12" t="s">
         <v>103</v>
       </c>
       <c r="H124" s="8" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="125" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A125" s="12" t="s">
         <v>104</v>
       </c>
@@ -4479,71 +4479,71 @@
         <v>411</v>
       </c>
     </row>
-    <row r="126" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A126" s="12" t="s">
         <v>105</v>
       </c>
       <c r="H126" s="8" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="127" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A127" s="12" t="s">
         <v>106</v>
       </c>
       <c r="H127" s="8" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="128" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A128" s="12" t="s">
         <v>107</v>
       </c>
       <c r="H128" s="8" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="129" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A129" s="12" t="s">
         <v>108</v>
       </c>
       <c r="H129" s="8" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="130" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A130" s="12" t="s">
         <v>109</v>
       </c>
       <c r="H130" s="8" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="131" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A131" s="12" t="s">
         <v>110</v>
       </c>
       <c r="H131" s="8" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="132" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A132" s="12" t="s">
         <v>111</v>
       </c>
       <c r="H132" s="8" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="133" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A133" s="12" t="s">
         <v>112</v>
       </c>
       <c r="H133" s="8" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="134" spans="1:9" s="9" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9" s="9" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B134" s="9" t="s">
         <v>372</v>
       </c>
@@ -4569,87 +4569,87 @@
         <v>375</v>
       </c>
     </row>
-    <row r="135" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A135" s="7" t="s">
         <v>362</v>
       </c>
       <c r="H135" s="8" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="136" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A136" s="7" t="s">
         <v>113</v>
       </c>
       <c r="H136" s="8" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="137" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A137" s="7" t="s">
         <v>114</v>
       </c>
       <c r="H137" s="8" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="138" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A138" s="7" t="s">
         <v>115</v>
       </c>
       <c r="H138" s="8" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="139" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A139" s="7" t="s">
         <v>116</v>
       </c>
       <c r="H139" s="8" t="s">
-        <v>736</v>
-      </c>
-    </row>
-    <row r="140" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A140" s="7" t="s">
         <v>117</v>
       </c>
       <c r="H140" s="8" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="141" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A141" s="7" t="s">
         <v>118</v>
       </c>
       <c r="H141" s="8" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="142" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A142" s="7" t="s">
         <v>119</v>
       </c>
       <c r="H142" s="8" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="143" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A143" s="7" t="s">
         <v>120</v>
       </c>
       <c r="H143" s="8" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="144" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A144" s="7" t="s">
         <v>121</v>
       </c>
       <c r="H144" s="8" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="145" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A145" s="7" t="s">
         <v>122</v>
       </c>
@@ -4657,23 +4657,23 @@
         <v>382</v>
       </c>
     </row>
-    <row r="146" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A146" s="7" t="s">
         <v>123</v>
       </c>
       <c r="H146" s="8" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="147" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A147" s="7" t="s">
         <v>124</v>
       </c>
       <c r="H147" s="8" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="148" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A148" s="7" t="s">
         <v>125</v>
       </c>
@@ -4681,15 +4681,15 @@
         <v>392</v>
       </c>
     </row>
-    <row r="149" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A149" s="7" t="s">
         <v>126</v>
       </c>
       <c r="H149" s="8" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="150" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A150" s="7" t="s">
         <v>127</v>
       </c>
@@ -4697,71 +4697,71 @@
         <v>383</v>
       </c>
     </row>
-    <row r="151" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A151" s="7" t="s">
         <v>128</v>
       </c>
       <c r="H151" s="8" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="152" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A152" s="7" t="s">
         <v>129</v>
       </c>
       <c r="H152" s="8" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="153" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A153" s="7" t="s">
         <v>130</v>
       </c>
       <c r="H153" s="8" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="154" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A154" s="7" t="s">
         <v>131</v>
       </c>
       <c r="H154" s="8" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="155" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A155" s="7" t="s">
         <v>132</v>
       </c>
       <c r="H155" s="8" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="156" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A156" s="7" t="s">
         <v>133</v>
       </c>
       <c r="H156" s="8" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="157" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A157" s="7" t="s">
         <v>134</v>
       </c>
       <c r="H157" s="8" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="158" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A158" s="7" t="s">
         <v>135</v>
       </c>
       <c r="H158" s="8" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="159" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A159" s="7" t="s">
         <v>136</v>
       </c>
@@ -4769,47 +4769,47 @@
         <v>384</v>
       </c>
     </row>
-    <row r="160" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A160" s="7" t="s">
         <v>137</v>
       </c>
       <c r="H160" s="8" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="161" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A161" s="7" t="s">
         <v>138</v>
       </c>
       <c r="H161" s="8" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="162" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A162" s="7" t="s">
         <v>139</v>
       </c>
       <c r="H162" s="8" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="163" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="163" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A163" s="7" t="s">
         <v>140</v>
       </c>
       <c r="H163" s="8" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="164" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="164" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A164" s="7" t="s">
         <v>141</v>
       </c>
       <c r="H164" s="8" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="165" spans="1:9" s="9" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="165" spans="1:9" s="9" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B165" s="9" t="s">
         <v>372</v>
       </c>
@@ -4835,180 +4835,180 @@
         <v>375</v>
       </c>
     </row>
-    <row r="166" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A166" s="10" t="s">
         <v>363</v>
       </c>
       <c r="H166" s="8" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="167" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="167" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A167" s="10" t="s">
         <v>364</v>
       </c>
       <c r="H167" s="8" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="168" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="168" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A168" s="10" t="s">
         <v>142</v>
       </c>
       <c r="H168" s="8" t="s">
-        <v>729</v>
-      </c>
-    </row>
-    <row r="169" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="169" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A169" s="10" t="s">
         <v>143</v>
       </c>
       <c r="H169" s="8" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="170" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="170" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A170" s="10" t="s">
         <v>144</v>
       </c>
       <c r="H170" s="8" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="171" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="171" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A171" s="10" t="s">
         <v>145</v>
       </c>
       <c r="H171" s="8" t="s">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="172" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="172" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A172" s="10" t="s">
         <v>146</v>
       </c>
       <c r="H172" s="8" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="173" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="173" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A173" s="10" t="s">
         <v>147</v>
       </c>
       <c r="H173" s="8" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="174" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="174" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A174" s="10" t="s">
         <v>148</v>
       </c>
       <c r="H174" s="8" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="175" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="175" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A175" s="10" t="s">
         <v>149</v>
       </c>
       <c r="H175" s="8" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="176" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="176" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A176" s="10" t="s">
         <v>150</v>
       </c>
       <c r="H176" s="8" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="177" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="177" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A177" s="10" t="s">
         <v>151</v>
       </c>
       <c r="H177" s="8" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="178" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="178" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A178" s="10" t="s">
         <v>152</v>
       </c>
       <c r="H178" s="8" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="179" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="179" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A179" s="10" t="s">
         <v>153</v>
       </c>
       <c r="H179" s="8" t="s">
-        <v>563</v>
-      </c>
-    </row>
-    <row r="180" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="180" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A180" s="10" t="s">
         <v>154</v>
       </c>
       <c r="H180" s="8" t="s">
-        <v>731</v>
-      </c>
-    </row>
-    <row r="181" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="181" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A181" s="10" t="s">
         <v>155</v>
       </c>
       <c r="H181" s="8" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="182" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="182" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A182" s="10" t="s">
         <v>156</v>
       </c>
       <c r="H182" s="8" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="183" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="183" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A183" s="10" t="s">
         <v>157</v>
       </c>
       <c r="H183" s="8" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="184" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="184" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A184" s="10" t="s">
         <v>158</v>
       </c>
       <c r="H184" s="8" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="185" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="185" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A185" s="10" t="s">
         <v>159</v>
       </c>
       <c r="H185" s="8" t="s">
-        <v>724</v>
-      </c>
-    </row>
-    <row r="186" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="186" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A186" s="10" t="s">
         <v>160</v>
       </c>
       <c r="H186" s="8" t="s">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="187" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="187" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A187" s="10" t="s">
         <v>161</v>
       </c>
       <c r="H187" s="8" t="s">
-        <v>727</v>
+        <v>721</v>
       </c>
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.4">
@@ -5016,7 +5016,7 @@
         <v>162</v>
       </c>
       <c r="H188" s="8" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.4">
@@ -5024,7 +5024,7 @@
         <v>163</v>
       </c>
       <c r="H189" s="8" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.4">
@@ -5032,7 +5032,7 @@
         <v>164</v>
       </c>
       <c r="H190" s="8" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.4">
@@ -5040,7 +5040,7 @@
         <v>165</v>
       </c>
       <c r="H191" s="8" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.4">
@@ -5048,7 +5048,7 @@
         <v>166</v>
       </c>
       <c r="H192" s="8" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
     </row>
     <row r="193" spans="1:9" x14ac:dyDescent="0.4">
@@ -5056,7 +5056,7 @@
         <v>167</v>
       </c>
       <c r="H193" s="8" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
     </row>
     <row r="194" spans="1:9" x14ac:dyDescent="0.4">
@@ -5064,7 +5064,7 @@
         <v>168</v>
       </c>
       <c r="H194" s="8" t="s">
-        <v>735</v>
+        <v>729</v>
       </c>
     </row>
     <row r="195" spans="1:9" x14ac:dyDescent="0.4">
@@ -5072,7 +5072,7 @@
         <v>169</v>
       </c>
       <c r="H195" s="8" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
     </row>
     <row r="196" spans="1:9" s="9" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -5106,7 +5106,7 @@
         <v>365</v>
       </c>
       <c r="H197" s="8" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
     </row>
     <row r="198" spans="1:9" x14ac:dyDescent="0.4">
@@ -5114,7 +5114,7 @@
         <v>170</v>
       </c>
       <c r="H198" s="8" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
     </row>
     <row r="199" spans="1:9" x14ac:dyDescent="0.4">
@@ -5122,7 +5122,7 @@
         <v>171</v>
       </c>
       <c r="H199" s="8" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
     </row>
     <row r="200" spans="1:9" x14ac:dyDescent="0.4">
@@ -5130,7 +5130,7 @@
         <v>172</v>
       </c>
       <c r="H200" s="8" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="201" spans="1:9" x14ac:dyDescent="0.4">
@@ -5138,7 +5138,7 @@
         <v>173</v>
       </c>
       <c r="H201" s="8" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
     </row>
     <row r="202" spans="1:9" x14ac:dyDescent="0.4">
@@ -5146,7 +5146,7 @@
         <v>174</v>
       </c>
       <c r="H202" s="8" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
     </row>
     <row r="203" spans="1:9" x14ac:dyDescent="0.4">
@@ -5154,7 +5154,7 @@
         <v>175</v>
       </c>
       <c r="H203" s="8" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
     </row>
     <row r="204" spans="1:9" x14ac:dyDescent="0.4">
@@ -5162,7 +5162,7 @@
         <v>176</v>
       </c>
       <c r="H204" s="8" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
     </row>
     <row r="205" spans="1:9" x14ac:dyDescent="0.4">
@@ -5170,7 +5170,7 @@
         <v>177</v>
       </c>
       <c r="H205" s="8" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
     </row>
     <row r="206" spans="1:9" x14ac:dyDescent="0.4">
@@ -5178,7 +5178,7 @@
         <v>178</v>
       </c>
       <c r="H206" s="8" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
     </row>
     <row r="207" spans="1:9" x14ac:dyDescent="0.4">
@@ -5186,7 +5186,7 @@
         <v>179</v>
       </c>
       <c r="H207" s="8" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
     </row>
     <row r="208" spans="1:9" x14ac:dyDescent="0.4">
@@ -5194,7 +5194,7 @@
         <v>180</v>
       </c>
       <c r="H208" s="8" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
     </row>
     <row r="209" spans="1:8" x14ac:dyDescent="0.4">
@@ -5202,7 +5202,7 @@
         <v>181</v>
       </c>
       <c r="H209" s="8" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
     </row>
     <row r="210" spans="1:8" x14ac:dyDescent="0.4">
@@ -5210,7 +5210,7 @@
         <v>182</v>
       </c>
       <c r="H210" s="8" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.4">
@@ -5218,7 +5218,7 @@
         <v>183</v>
       </c>
       <c r="H211" s="8" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
     </row>
     <row r="212" spans="1:8" x14ac:dyDescent="0.4">
@@ -5226,7 +5226,7 @@
         <v>184</v>
       </c>
       <c r="H212" s="8" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
     </row>
     <row r="213" spans="1:8" x14ac:dyDescent="0.4">
@@ -5234,7 +5234,7 @@
         <v>185</v>
       </c>
       <c r="H213" s="8" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
     </row>
     <row r="214" spans="1:8" x14ac:dyDescent="0.4">
@@ -5242,7 +5242,7 @@
         <v>186</v>
       </c>
       <c r="H214" s="8" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
     </row>
     <row r="215" spans="1:8" x14ac:dyDescent="0.4">
@@ -5250,7 +5250,7 @@
         <v>187</v>
       </c>
       <c r="H215" s="8" t="s">
-        <v>737</v>
+        <v>731</v>
       </c>
     </row>
     <row r="216" spans="1:8" x14ac:dyDescent="0.4">
@@ -5258,7 +5258,7 @@
         <v>188</v>
       </c>
       <c r="H216" s="8" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
     </row>
     <row r="217" spans="1:8" x14ac:dyDescent="0.4">
@@ -5266,7 +5266,7 @@
         <v>189</v>
       </c>
       <c r="H217" s="8" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="218" spans="1:8" x14ac:dyDescent="0.4">
@@ -5274,7 +5274,7 @@
         <v>190</v>
       </c>
       <c r="H218" s="8" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
     </row>
     <row r="219" spans="1:8" x14ac:dyDescent="0.4">
@@ -5282,7 +5282,7 @@
         <v>191</v>
       </c>
       <c r="H219" s="8" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
     </row>
     <row r="220" spans="1:8" x14ac:dyDescent="0.4">
@@ -5290,7 +5290,7 @@
         <v>192</v>
       </c>
       <c r="H220" s="8" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
     </row>
     <row r="221" spans="1:8" x14ac:dyDescent="0.4">
@@ -5298,7 +5298,7 @@
         <v>193</v>
       </c>
       <c r="H221" s="8" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
     </row>
     <row r="222" spans="1:8" x14ac:dyDescent="0.4">
@@ -5322,7 +5322,7 @@
         <v>196</v>
       </c>
       <c r="H224" s="8" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
     </row>
     <row r="225" spans="1:9" x14ac:dyDescent="0.4">
@@ -5338,7 +5338,7 @@
         <v>198</v>
       </c>
       <c r="H226" s="8" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
     </row>
     <row r="227" spans="1:9" s="9" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -5372,7 +5372,7 @@
         <v>366</v>
       </c>
       <c r="H228" s="8" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
     </row>
     <row r="229" spans="1:9" x14ac:dyDescent="0.4">
@@ -5380,7 +5380,7 @@
         <v>199</v>
       </c>
       <c r="H229" s="8" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
     </row>
     <row r="230" spans="1:9" x14ac:dyDescent="0.4">
@@ -5388,7 +5388,7 @@
         <v>200</v>
       </c>
       <c r="H230" s="8" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
     </row>
     <row r="231" spans="1:9" x14ac:dyDescent="0.4">
@@ -5396,7 +5396,7 @@
         <v>201</v>
       </c>
       <c r="H231" s="8" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
     </row>
     <row r="232" spans="1:9" x14ac:dyDescent="0.4">
@@ -5404,7 +5404,7 @@
         <v>202</v>
       </c>
       <c r="H232" s="8" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
     </row>
     <row r="233" spans="1:9" x14ac:dyDescent="0.4">
@@ -5412,7 +5412,7 @@
         <v>203</v>
       </c>
       <c r="H233" s="8" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="234" spans="1:9" x14ac:dyDescent="0.4">
@@ -5420,7 +5420,7 @@
         <v>204</v>
       </c>
       <c r="H234" s="8" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
     </row>
     <row r="235" spans="1:9" x14ac:dyDescent="0.4">
@@ -5428,7 +5428,7 @@
         <v>205</v>
       </c>
       <c r="H235" s="8" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
     </row>
     <row r="236" spans="1:9" x14ac:dyDescent="0.4">
@@ -5436,7 +5436,7 @@
         <v>206</v>
       </c>
       <c r="H236" s="8" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
     </row>
     <row r="237" spans="1:9" x14ac:dyDescent="0.4">
@@ -5444,7 +5444,7 @@
         <v>207</v>
       </c>
       <c r="H237" s="8" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="238" spans="1:9" x14ac:dyDescent="0.4">
@@ -5452,7 +5452,7 @@
         <v>208</v>
       </c>
       <c r="H238" s="8" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
     </row>
     <row r="239" spans="1:9" x14ac:dyDescent="0.4">
@@ -5460,7 +5460,7 @@
         <v>209</v>
       </c>
       <c r="H239" s="8" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
     </row>
     <row r="240" spans="1:9" x14ac:dyDescent="0.4">
@@ -5468,7 +5468,7 @@
         <v>210</v>
       </c>
       <c r="H240" s="8" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
     </row>
     <row r="241" spans="1:8" x14ac:dyDescent="0.4">
@@ -5476,7 +5476,7 @@
         <v>211</v>
       </c>
       <c r="H241" s="8" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
     </row>
     <row r="242" spans="1:8" x14ac:dyDescent="0.4">
@@ -5484,7 +5484,7 @@
         <v>212</v>
       </c>
       <c r="H242" s="8" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
     </row>
     <row r="243" spans="1:8" x14ac:dyDescent="0.4">
@@ -5492,7 +5492,7 @@
         <v>213</v>
       </c>
       <c r="H243" s="8" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
     </row>
     <row r="244" spans="1:8" x14ac:dyDescent="0.4">
@@ -5500,7 +5500,7 @@
         <v>214</v>
       </c>
       <c r="H244" s="8" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
     </row>
     <row r="245" spans="1:8" x14ac:dyDescent="0.4">
@@ -5508,7 +5508,7 @@
         <v>215</v>
       </c>
       <c r="H245" s="8" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
     </row>
     <row r="246" spans="1:8" x14ac:dyDescent="0.4">
@@ -5516,7 +5516,7 @@
         <v>216</v>
       </c>
       <c r="H246" s="8" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
     </row>
     <row r="247" spans="1:8" x14ac:dyDescent="0.4">
@@ -5524,7 +5524,7 @@
         <v>217</v>
       </c>
       <c r="H247" s="8" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
     </row>
     <row r="248" spans="1:8" x14ac:dyDescent="0.4">
@@ -5532,7 +5532,7 @@
         <v>218</v>
       </c>
       <c r="H248" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="249" spans="1:8" x14ac:dyDescent="0.4">
@@ -5540,7 +5540,7 @@
         <v>219</v>
       </c>
       <c r="H249" s="8" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
     </row>
     <row r="250" spans="1:8" x14ac:dyDescent="0.4">
@@ -5548,7 +5548,7 @@
         <v>220</v>
       </c>
       <c r="H250" s="8" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
     </row>
     <row r="251" spans="1:8" x14ac:dyDescent="0.4">
@@ -5556,7 +5556,7 @@
         <v>221</v>
       </c>
       <c r="H251" s="8" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
     </row>
     <row r="252" spans="1:8" x14ac:dyDescent="0.4">
@@ -5564,7 +5564,7 @@
         <v>222</v>
       </c>
       <c r="H252" s="8" t="s">
-        <v>622</v>
+        <v>618</v>
       </c>
     </row>
     <row r="253" spans="1:8" x14ac:dyDescent="0.4">
@@ -5572,7 +5572,7 @@
         <v>223</v>
       </c>
       <c r="H253" s="8" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="254" spans="1:8" x14ac:dyDescent="0.4">
@@ -5580,7 +5580,7 @@
         <v>224</v>
       </c>
       <c r="H254" s="8" t="s">
-        <v>624</v>
+        <v>620</v>
       </c>
     </row>
     <row r="255" spans="1:8" x14ac:dyDescent="0.4">
@@ -5588,7 +5588,7 @@
         <v>225</v>
       </c>
       <c r="H255" s="8" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
     </row>
     <row r="256" spans="1:8" x14ac:dyDescent="0.4">
@@ -5596,7 +5596,7 @@
         <v>226</v>
       </c>
       <c r="H256" s="8" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
     </row>
     <row r="257" spans="1:9" x14ac:dyDescent="0.4">
@@ -5604,7 +5604,7 @@
         <v>227</v>
       </c>
       <c r="H257" s="8" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
     </row>
     <row r="258" spans="1:9" s="9" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -5638,7 +5638,7 @@
         <v>367</v>
       </c>
       <c r="H259" s="8" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
     </row>
     <row r="260" spans="1:9" x14ac:dyDescent="0.4">
@@ -5646,7 +5646,7 @@
         <v>228</v>
       </c>
       <c r="H260" s="8" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
     </row>
     <row r="261" spans="1:9" x14ac:dyDescent="0.4">
@@ -5654,7 +5654,7 @@
         <v>229</v>
       </c>
       <c r="H261" s="8" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
     </row>
     <row r="262" spans="1:9" x14ac:dyDescent="0.4">
@@ -5662,7 +5662,7 @@
         <v>230</v>
       </c>
       <c r="H262" s="8" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="263" spans="1:9" x14ac:dyDescent="0.4">
@@ -5670,7 +5670,7 @@
         <v>231</v>
       </c>
       <c r="H263" s="8" t="s">
-        <v>723</v>
+        <v>717</v>
       </c>
     </row>
     <row r="264" spans="1:9" x14ac:dyDescent="0.4">
@@ -5678,7 +5678,7 @@
         <v>232</v>
       </c>
       <c r="H264" s="8" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
     </row>
     <row r="265" spans="1:9" x14ac:dyDescent="0.4">
@@ -5686,7 +5686,7 @@
         <v>233</v>
       </c>
       <c r="H265" s="8" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
     </row>
     <row r="266" spans="1:9" x14ac:dyDescent="0.4">
@@ -5694,7 +5694,7 @@
         <v>234</v>
       </c>
       <c r="H266" s="8" t="s">
-        <v>633</v>
+        <v>629</v>
       </c>
     </row>
     <row r="267" spans="1:9" x14ac:dyDescent="0.4">
@@ -5702,7 +5702,7 @@
         <v>235</v>
       </c>
       <c r="H267" s="8" t="s">
-        <v>634</v>
+        <v>630</v>
       </c>
     </row>
     <row r="268" spans="1:9" x14ac:dyDescent="0.4">
@@ -5710,7 +5710,7 @@
         <v>0</v>
       </c>
       <c r="H268" s="8" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
     </row>
     <row r="269" spans="1:9" x14ac:dyDescent="0.4">
@@ -5718,7 +5718,7 @@
         <v>236</v>
       </c>
       <c r="H269" s="8" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
     </row>
     <row r="270" spans="1:9" x14ac:dyDescent="0.4">
@@ -5726,7 +5726,7 @@
         <v>237</v>
       </c>
       <c r="H270" s="8" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
     </row>
     <row r="271" spans="1:9" x14ac:dyDescent="0.4">
@@ -5734,7 +5734,7 @@
         <v>238</v>
       </c>
       <c r="H271" s="8" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
     </row>
     <row r="272" spans="1:9" x14ac:dyDescent="0.4">
@@ -5742,7 +5742,7 @@
         <v>239</v>
       </c>
       <c r="H272" s="8" t="s">
-        <v>639</v>
+        <v>635</v>
       </c>
     </row>
     <row r="273" spans="1:8" x14ac:dyDescent="0.4">
@@ -5758,7 +5758,7 @@
         <v>241</v>
       </c>
       <c r="H274" s="8" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
     </row>
     <row r="275" spans="1:8" x14ac:dyDescent="0.4">
@@ -5766,7 +5766,7 @@
         <v>242</v>
       </c>
       <c r="H275" s="8" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
     </row>
     <row r="276" spans="1:8" x14ac:dyDescent="0.4">
@@ -5774,7 +5774,7 @@
         <v>243</v>
       </c>
       <c r="H276" s="8" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
     </row>
     <row r="277" spans="1:8" x14ac:dyDescent="0.4">
@@ -5782,7 +5782,7 @@
         <v>244</v>
       </c>
       <c r="H277" s="8" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="278" spans="1:8" x14ac:dyDescent="0.4">
@@ -5790,7 +5790,7 @@
         <v>245</v>
       </c>
       <c r="H278" s="8" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
     </row>
     <row r="279" spans="1:8" x14ac:dyDescent="0.4">
@@ -5806,7 +5806,7 @@
         <v>247</v>
       </c>
       <c r="H280" s="8" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
     </row>
     <row r="281" spans="1:8" x14ac:dyDescent="0.4">
@@ -5814,7 +5814,7 @@
         <v>248</v>
       </c>
       <c r="H281" s="8" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
     </row>
     <row r="282" spans="1:8" x14ac:dyDescent="0.4">
@@ -5822,7 +5822,7 @@
         <v>249</v>
       </c>
       <c r="H282" s="8" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
     </row>
     <row r="283" spans="1:8" x14ac:dyDescent="0.4">
@@ -5838,7 +5838,7 @@
         <v>251</v>
       </c>
       <c r="H284" s="8" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="285" spans="1:8" x14ac:dyDescent="0.4">
@@ -5846,7 +5846,7 @@
         <v>252</v>
       </c>
       <c r="H285" s="8" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
     </row>
     <row r="286" spans="1:8" x14ac:dyDescent="0.4">
@@ -5854,7 +5854,7 @@
         <v>253</v>
       </c>
       <c r="H286" s="8" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
     </row>
     <row r="287" spans="1:8" x14ac:dyDescent="0.4">
@@ -5862,7 +5862,7 @@
         <v>254</v>
       </c>
       <c r="H287" s="8" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
     </row>
     <row r="288" spans="1:8" x14ac:dyDescent="0.4">
@@ -5870,7 +5870,7 @@
         <v>255</v>
       </c>
       <c r="H288" s="8" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
     </row>
     <row r="289" spans="1:9" s="9" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -5904,7 +5904,7 @@
         <v>368</v>
       </c>
       <c r="H290" s="8" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
     </row>
     <row r="291" spans="1:9" x14ac:dyDescent="0.4">
@@ -5912,7 +5912,7 @@
         <v>256</v>
       </c>
       <c r="H291" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
     </row>
     <row r="292" spans="1:9" x14ac:dyDescent="0.4">
@@ -5928,7 +5928,7 @@
         <v>258</v>
       </c>
       <c r="H293" s="8" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="294" spans="1:9" x14ac:dyDescent="0.4">
@@ -5936,7 +5936,7 @@
         <v>259</v>
       </c>
       <c r="H294" s="8" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
     </row>
     <row r="295" spans="1:9" x14ac:dyDescent="0.4">
@@ -5944,7 +5944,7 @@
         <v>260</v>
       </c>
       <c r="H295" s="8" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
     </row>
     <row r="296" spans="1:9" x14ac:dyDescent="0.4">
@@ -5952,7 +5952,7 @@
         <v>261</v>
       </c>
       <c r="H296" s="8" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
     </row>
     <row r="297" spans="1:9" x14ac:dyDescent="0.4">
@@ -5960,7 +5960,7 @@
         <v>262</v>
       </c>
       <c r="H297" s="8" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
     </row>
     <row r="298" spans="1:9" x14ac:dyDescent="0.4">
@@ -5968,7 +5968,7 @@
         <v>263</v>
       </c>
       <c r="H298" s="8" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
     </row>
     <row r="299" spans="1:9" x14ac:dyDescent="0.4">
@@ -5976,7 +5976,7 @@
         <v>264</v>
       </c>
       <c r="H299" s="8" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
     </row>
     <row r="300" spans="1:9" x14ac:dyDescent="0.4">
@@ -5984,7 +5984,7 @@
         <v>265</v>
       </c>
       <c r="H300" s="8" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
     </row>
     <row r="301" spans="1:9" x14ac:dyDescent="0.4">
@@ -5992,7 +5992,7 @@
         <v>266</v>
       </c>
       <c r="H301" s="8" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
     </row>
     <row r="302" spans="1:9" x14ac:dyDescent="0.4">
@@ -6000,7 +6000,7 @@
         <v>267</v>
       </c>
       <c r="H302" s="8" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
     </row>
     <row r="303" spans="1:9" x14ac:dyDescent="0.4">
@@ -6008,7 +6008,7 @@
         <v>268</v>
       </c>
       <c r="H303" s="8" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="304" spans="1:9" x14ac:dyDescent="0.4">
@@ -6016,7 +6016,7 @@
         <v>269</v>
       </c>
       <c r="H304" s="8" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
     </row>
     <row r="305" spans="1:9" x14ac:dyDescent="0.4">
@@ -6024,7 +6024,7 @@
         <v>270</v>
       </c>
       <c r="H305" s="8" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
     </row>
     <row r="306" spans="1:9" x14ac:dyDescent="0.4">
@@ -6032,7 +6032,7 @@
         <v>271</v>
       </c>
       <c r="H306" s="8" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
     </row>
     <row r="307" spans="1:9" x14ac:dyDescent="0.4">
@@ -6040,7 +6040,7 @@
         <v>272</v>
       </c>
       <c r="H307" s="8" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
     </row>
     <row r="308" spans="1:9" x14ac:dyDescent="0.4">
@@ -6056,7 +6056,7 @@
         <v>274</v>
       </c>
       <c r="H309" s="8" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
     </row>
     <row r="310" spans="1:9" x14ac:dyDescent="0.4">
@@ -6064,7 +6064,7 @@
         <v>275</v>
       </c>
       <c r="H310" s="8" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
     </row>
     <row r="311" spans="1:9" x14ac:dyDescent="0.4">
@@ -6072,7 +6072,7 @@
         <v>276</v>
       </c>
       <c r="H311" s="8" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="312" spans="1:9" x14ac:dyDescent="0.4">
@@ -6080,7 +6080,7 @@
         <v>277</v>
       </c>
       <c r="H312" s="8" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
     </row>
     <row r="313" spans="1:9" x14ac:dyDescent="0.4">
@@ -6088,7 +6088,7 @@
         <v>278</v>
       </c>
       <c r="H313" s="8" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
     </row>
     <row r="314" spans="1:9" x14ac:dyDescent="0.4">
@@ -6096,7 +6096,7 @@
         <v>279</v>
       </c>
       <c r="H314" s="8" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
     </row>
     <row r="315" spans="1:9" x14ac:dyDescent="0.4">
@@ -6104,7 +6104,7 @@
         <v>280</v>
       </c>
       <c r="H315" s="8" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
     </row>
     <row r="316" spans="1:9" x14ac:dyDescent="0.4">
@@ -6112,7 +6112,7 @@
         <v>281</v>
       </c>
       <c r="H316" s="8" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
     </row>
     <row r="317" spans="1:9" x14ac:dyDescent="0.4">
@@ -6120,7 +6120,7 @@
         <v>282</v>
       </c>
       <c r="H317" s="8" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
     </row>
     <row r="318" spans="1:9" x14ac:dyDescent="0.4">
@@ -6128,7 +6128,7 @@
         <v>283</v>
       </c>
       <c r="H318" s="8" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="319" spans="1:9" x14ac:dyDescent="0.4">
@@ -6136,7 +6136,7 @@
         <v>284</v>
       </c>
       <c r="H319" s="8" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
     </row>
     <row r="320" spans="1:9" s="9" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -6170,7 +6170,7 @@
         <v>369</v>
       </c>
       <c r="H321" s="8" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
     </row>
     <row r="322" spans="1:8" x14ac:dyDescent="0.4">
@@ -6178,7 +6178,7 @@
         <v>285</v>
       </c>
       <c r="H322" s="8" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
     </row>
     <row r="323" spans="1:8" x14ac:dyDescent="0.4">
@@ -6186,7 +6186,7 @@
         <v>286</v>
       </c>
       <c r="H323" s="8" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
     </row>
     <row r="324" spans="1:8" x14ac:dyDescent="0.4">
@@ -6194,7 +6194,7 @@
         <v>287</v>
       </c>
       <c r="H324" s="8" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="325" spans="1:8" x14ac:dyDescent="0.4">
@@ -6202,7 +6202,7 @@
         <v>288</v>
       </c>
       <c r="H325" s="8" t="s">
-        <v>676</v>
+        <v>672</v>
       </c>
     </row>
     <row r="326" spans="1:8" x14ac:dyDescent="0.4">
@@ -6210,7 +6210,7 @@
         <v>289</v>
       </c>
       <c r="H326" s="8" t="s">
-        <v>677</v>
+        <v>673</v>
       </c>
     </row>
     <row r="327" spans="1:8" x14ac:dyDescent="0.4">
@@ -6218,7 +6218,7 @@
         <v>290</v>
       </c>
       <c r="H327" s="8" t="s">
-        <v>678</v>
+        <v>674</v>
       </c>
     </row>
     <row r="328" spans="1:8" x14ac:dyDescent="0.4">
@@ -6226,7 +6226,7 @@
         <v>291</v>
       </c>
       <c r="H328" s="8" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
     </row>
     <row r="329" spans="1:8" x14ac:dyDescent="0.4">
@@ -6234,7 +6234,7 @@
         <v>292</v>
       </c>
       <c r="H329" s="8" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
     </row>
     <row r="330" spans="1:8" x14ac:dyDescent="0.4">
@@ -6242,7 +6242,7 @@
         <v>293</v>
       </c>
       <c r="H330" s="8" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
     </row>
     <row r="331" spans="1:8" x14ac:dyDescent="0.4">
@@ -6258,7 +6258,7 @@
         <v>295</v>
       </c>
       <c r="H332" s="8" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
     </row>
     <row r="333" spans="1:8" x14ac:dyDescent="0.4">
@@ -6266,7 +6266,7 @@
         <v>296</v>
       </c>
       <c r="H333" s="8" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="334" spans="1:8" x14ac:dyDescent="0.4">
@@ -6274,7 +6274,7 @@
         <v>297</v>
       </c>
       <c r="H334" s="8" t="s">
-        <v>683</v>
+        <v>679</v>
       </c>
     </row>
     <row r="335" spans="1:8" x14ac:dyDescent="0.4">
@@ -6282,7 +6282,7 @@
         <v>298</v>
       </c>
       <c r="H335" s="8" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
     </row>
     <row r="336" spans="1:8" x14ac:dyDescent="0.4">
@@ -6290,7 +6290,7 @@
         <v>299</v>
       </c>
       <c r="H336" s="8" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
     </row>
     <row r="337" spans="1:9" x14ac:dyDescent="0.4">
@@ -6298,7 +6298,7 @@
         <v>300</v>
       </c>
       <c r="H337" s="8" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
     </row>
     <row r="338" spans="1:9" x14ac:dyDescent="0.4">
@@ -6306,7 +6306,7 @@
         <v>301</v>
       </c>
       <c r="H338" s="8" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
     </row>
     <row r="339" spans="1:9" x14ac:dyDescent="0.4">
@@ -6314,7 +6314,7 @@
         <v>302</v>
       </c>
       <c r="H339" s="8" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
     </row>
     <row r="340" spans="1:9" x14ac:dyDescent="0.4">
@@ -6322,7 +6322,7 @@
         <v>303</v>
       </c>
       <c r="H340" s="8" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
     </row>
     <row r="341" spans="1:9" x14ac:dyDescent="0.4">
@@ -6330,7 +6330,7 @@
         <v>304</v>
       </c>
       <c r="H341" s="8" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
     </row>
     <row r="342" spans="1:9" x14ac:dyDescent="0.4">
@@ -6338,7 +6338,7 @@
         <v>305</v>
       </c>
       <c r="H342" s="8" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
     </row>
     <row r="343" spans="1:9" x14ac:dyDescent="0.4">
@@ -6354,7 +6354,7 @@
         <v>307</v>
       </c>
       <c r="H344" s="8" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="345" spans="1:9" x14ac:dyDescent="0.4">
@@ -6370,7 +6370,7 @@
         <v>309</v>
       </c>
       <c r="H346" s="8" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
     </row>
     <row r="347" spans="1:9" x14ac:dyDescent="0.4">
@@ -6386,7 +6386,7 @@
         <v>311</v>
       </c>
       <c r="H348" s="8" t="s">
-        <v>429</v>
+        <v>734</v>
       </c>
     </row>
     <row r="349" spans="1:9" x14ac:dyDescent="0.4">
@@ -6394,7 +6394,7 @@
         <v>312</v>
       </c>
       <c r="H349" s="8" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
     </row>
     <row r="350" spans="1:9" x14ac:dyDescent="0.4">
@@ -6436,7 +6436,7 @@
         <v>370</v>
       </c>
       <c r="H352" s="8" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
     </row>
     <row r="353" spans="1:8" x14ac:dyDescent="0.4">
@@ -6444,7 +6444,7 @@
         <v>314</v>
       </c>
       <c r="H353" s="8" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="354" spans="1:8" x14ac:dyDescent="0.4">
@@ -6452,7 +6452,7 @@
         <v>315</v>
       </c>
       <c r="H354" s="8" t="s">
-        <v>695</v>
+        <v>691</v>
       </c>
     </row>
     <row r="355" spans="1:8" x14ac:dyDescent="0.4">
@@ -6460,7 +6460,7 @@
         <v>316</v>
       </c>
       <c r="H355" s="8" t="s">
-        <v>696</v>
+        <v>692</v>
       </c>
     </row>
     <row r="356" spans="1:8" x14ac:dyDescent="0.4">
@@ -6468,7 +6468,7 @@
         <v>317</v>
       </c>
       <c r="H356" s="8" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="357" spans="1:8" x14ac:dyDescent="0.4">
@@ -6476,7 +6476,7 @@
         <v>318</v>
       </c>
       <c r="H357" s="8" t="s">
-        <v>697</v>
+        <v>693</v>
       </c>
     </row>
     <row r="358" spans="1:8" x14ac:dyDescent="0.4">
@@ -6484,7 +6484,7 @@
         <v>319</v>
       </c>
       <c r="H358" s="8" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="359" spans="1:8" x14ac:dyDescent="0.4">
@@ -6492,7 +6492,7 @@
         <v>320</v>
       </c>
       <c r="H359" s="8" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
     </row>
     <row r="360" spans="1:8" x14ac:dyDescent="0.4">
@@ -6500,7 +6500,7 @@
         <v>321</v>
       </c>
       <c r="H360" s="8" t="s">
-        <v>700</v>
+        <v>696</v>
       </c>
     </row>
     <row r="361" spans="1:8" x14ac:dyDescent="0.4">
@@ -6508,7 +6508,7 @@
         <v>322</v>
       </c>
       <c r="H361" s="8" t="s">
-        <v>701</v>
+        <v>697</v>
       </c>
     </row>
     <row r="362" spans="1:8" x14ac:dyDescent="0.4">
@@ -6516,7 +6516,7 @@
         <v>323</v>
       </c>
       <c r="H362" s="8" t="s">
-        <v>702</v>
+        <v>698</v>
       </c>
     </row>
     <row r="363" spans="1:8" x14ac:dyDescent="0.4">
@@ -6524,7 +6524,7 @@
         <v>324</v>
       </c>
       <c r="H363" s="8" t="s">
-        <v>703</v>
+        <v>699</v>
       </c>
     </row>
     <row r="364" spans="1:8" x14ac:dyDescent="0.4">
@@ -6532,7 +6532,7 @@
         <v>325</v>
       </c>
       <c r="H364" s="8" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
     </row>
     <row r="365" spans="1:8" x14ac:dyDescent="0.4">
@@ -6540,7 +6540,7 @@
         <v>326</v>
       </c>
       <c r="H365" s="8" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
     </row>
     <row r="366" spans="1:8" x14ac:dyDescent="0.4">
@@ -6548,7 +6548,7 @@
         <v>327</v>
       </c>
       <c r="H366" s="8" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
     </row>
     <row r="367" spans="1:8" x14ac:dyDescent="0.4">
@@ -6556,7 +6556,7 @@
         <v>328</v>
       </c>
       <c r="H367" s="8" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="368" spans="1:8" x14ac:dyDescent="0.4">
@@ -6564,7 +6564,7 @@
         <v>329</v>
       </c>
       <c r="H368" s="8" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
     </row>
     <row r="369" spans="1:9" x14ac:dyDescent="0.4">
@@ -6572,7 +6572,7 @@
         <v>330</v>
       </c>
       <c r="H369" s="8" t="s">
-        <v>709</v>
+        <v>735</v>
       </c>
     </row>
     <row r="370" spans="1:9" x14ac:dyDescent="0.4">
@@ -6580,7 +6580,7 @@
         <v>331</v>
       </c>
       <c r="H370" s="8" t="s">
-        <v>710</v>
+        <v>705</v>
       </c>
     </row>
     <row r="371" spans="1:9" x14ac:dyDescent="0.4">
@@ -6588,7 +6588,7 @@
         <v>332</v>
       </c>
       <c r="H371" s="8" t="s">
-        <v>711</v>
+        <v>706</v>
       </c>
     </row>
     <row r="372" spans="1:9" x14ac:dyDescent="0.4">
@@ -6596,7 +6596,7 @@
         <v>333</v>
       </c>
       <c r="H372" s="8" t="s">
-        <v>712</v>
+        <v>707</v>
       </c>
     </row>
     <row r="373" spans="1:9" x14ac:dyDescent="0.4">
@@ -6604,7 +6604,7 @@
         <v>334</v>
       </c>
       <c r="H373" s="8" t="s">
-        <v>713</v>
+        <v>708</v>
       </c>
     </row>
     <row r="374" spans="1:9" x14ac:dyDescent="0.4">
@@ -6612,7 +6612,7 @@
         <v>335</v>
       </c>
       <c r="H374" s="8" t="s">
-        <v>714</v>
+        <v>709</v>
       </c>
     </row>
     <row r="375" spans="1:9" x14ac:dyDescent="0.4">
@@ -6620,7 +6620,7 @@
         <v>336</v>
       </c>
       <c r="H375" s="8" t="s">
-        <v>715</v>
+        <v>736</v>
       </c>
     </row>
     <row r="376" spans="1:9" x14ac:dyDescent="0.4">
@@ -6628,7 +6628,7 @@
         <v>337</v>
       </c>
       <c r="H376" s="8" t="s">
-        <v>716</v>
+        <v>710</v>
       </c>
     </row>
     <row r="377" spans="1:9" x14ac:dyDescent="0.4">
@@ -6636,7 +6636,7 @@
         <v>338</v>
       </c>
       <c r="H377" s="8" t="s">
-        <v>721</v>
+        <v>715</v>
       </c>
     </row>
     <row r="378" spans="1:9" x14ac:dyDescent="0.4">
@@ -6644,7 +6644,7 @@
         <v>339</v>
       </c>
       <c r="H378" s="8" t="s">
-        <v>720</v>
+        <v>714</v>
       </c>
     </row>
     <row r="379" spans="1:9" x14ac:dyDescent="0.4">
@@ -6652,7 +6652,7 @@
         <v>340</v>
       </c>
       <c r="H379" s="8" t="s">
-        <v>719</v>
+        <v>713</v>
       </c>
     </row>
     <row r="380" spans="1:9" x14ac:dyDescent="0.4">
@@ -6660,7 +6660,7 @@
         <v>341</v>
       </c>
       <c r="H380" s="8" t="s">
-        <v>718</v>
+        <v>712</v>
       </c>
     </row>
     <row r="381" spans="1:9" x14ac:dyDescent="0.4">
@@ -6668,7 +6668,7 @@
         <v>342</v>
       </c>
       <c r="H381" s="8" t="s">
-        <v>717</v>
+        <v>711</v>
       </c>
     </row>
     <row r="382" spans="1:9" s="9" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
